--- a/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
   <si>
     <t>EVBN</t>
   </si>
@@ -656,232 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E8" s="3">
         <v>24300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>19100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>17500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>16000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>14700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>13400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>12800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>10900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1443,7 +1465,7 @@
         <v>-100</v>
       </c>
       <c r="Y15" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Z15" s="3">
         <v>0</v>
@@ -1463,11 +1485,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E17" s="3">
         <v>10500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>500</v>
-      </c>
-      <c r="N17" s="3">
-        <v>1700</v>
       </c>
       <c r="O17" s="3">
         <v>1700</v>
       </c>
       <c r="P17" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="Q17" s="3">
         <v>2100</v>
       </c>
       <c r="R17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S17" s="3">
         <v>3800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2900</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>2700</v>
       </c>
       <c r="Z17" s="3">
         <v>2700</v>
       </c>
       <c r="AA17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AB17" s="3">
         <v>2200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E18" s="3">
         <v>13800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>17900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>11900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1747,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-9500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-10400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-14400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-7100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-7400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E21" s="3">
         <v>5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>8200</v>
       </c>
       <c r="H21" s="3">
         <v>8200</v>
       </c>
       <c r="I21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J21" s="3">
         <v>8000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>6700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>7400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>4700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>3600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>5000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E23" s="3">
         <v>4900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>5600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>1800</v>
       </c>
       <c r="G24" s="3">
         <v>1800</v>
       </c>
       <c r="H24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I24" s="3">
         <v>2000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
-      </c>
-      <c r="U24" s="3">
-        <v>1200</v>
       </c>
       <c r="V24" s="3">
         <v>1200</v>
       </c>
       <c r="W24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="X24" s="3">
         <v>-200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E26" s="3">
         <v>3600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>3700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>5200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E27" s="3">
         <v>3600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,17 +2659,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2617,12 +2677,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E32" s="3">
         <v>8900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>9500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>10400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>14400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>7100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>6700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>7400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E33" s="3">
         <v>3600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>1000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E35" s="3">
         <v>3600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>1000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,192 +3437,199 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E41" s="3">
         <v>17800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>15200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>10600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>10600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>15400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>10600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>13300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>16800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>10800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E42" s="3">
         <v>13900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>17400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>12300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>19800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>13500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>94000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>153100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>241000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>185500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>133100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>112000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>89700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>94200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>115700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>44300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>31800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>18300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>49200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>59500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>29300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>18900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>6800</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>14500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>14400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>5600</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>22400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,8 +4005,11 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3996,174 +4100,180 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E48" s="3">
         <v>19900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>22200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>22600</v>
-      </c>
-      <c r="R48" s="3">
-        <v>17500</v>
       </c>
       <c r="S48" s="3">
         <v>17500</v>
       </c>
       <c r="T48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="U48" s="3">
         <v>17800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E49" s="3">
         <v>13600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>13700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>14000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>13400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>12500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>13000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13100</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>8500</v>
       </c>
       <c r="Z49" s="3">
         <v>8500</v>
       </c>
       <c r="AA49" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="AB49" s="3">
         <v>8600</v>
@@ -4175,13 +4285,16 @@
         <v>8600</v>
       </c>
       <c r="AE49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AF49" s="3">
         <v>8400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4480,11 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4456,8 +4575,11 @@
       <c r="AF52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2108700</v>
+      </c>
+      <c r="E54" s="3">
         <v>2174700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2155000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2148300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2178500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2129700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2208400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2240700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2210600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2152100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2160200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2144300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2044100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2057000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2065900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1524800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1460200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1455700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1471100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1456200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1388200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1380900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1346100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1353700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1295600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1220200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1182800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1139700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1100700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1084700</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,8 +4930,11 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,71 +5025,74 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E59" s="3">
         <v>4400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4600</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4966,8 +5102,8 @@
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -4984,8 +5120,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,8 +5215,11 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5085,7 +5227,7 @@
         <v>31200</v>
       </c>
       <c r="E61" s="3">
-        <v>31100</v>
+        <v>31200</v>
       </c>
       <c r="F61" s="3">
         <v>31100</v>
@@ -5097,7 +5239,7 @@
         <v>31100</v>
       </c>
       <c r="I61" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="J61" s="3">
         <v>31000</v>
@@ -5106,7 +5248,7 @@
         <v>31000</v>
       </c>
       <c r="L61" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="M61" s="3">
         <v>30900</v>
@@ -5121,7 +5263,7 @@
         <v>30900</v>
       </c>
       <c r="Q61" s="3">
-        <v>11300</v>
+        <v>30900</v>
       </c>
       <c r="R61" s="3">
         <v>11300</v>
@@ -5160,16 +5302,19 @@
         <v>11300</v>
       </c>
       <c r="AD61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AE61" s="3">
         <v>21300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>39500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>62500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1930400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2023800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1995500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1990000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2024500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1979900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2045700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2071500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2026700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1973200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1984500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1977300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1875200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1894100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1903900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1376700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1311800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1310900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1329800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1321700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1256600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1255300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1222500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1233800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1177300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1102700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1067300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1027000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1004000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>989500</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>128500</v>
+        <v>138600</v>
       </c>
       <c r="E72" s="3">
         <v>128500</v>
       </c>
       <c r="F72" s="3">
+        <v>128500</v>
+      </c>
+      <c r="G72" s="3">
         <v>123500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>123400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>117300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>115000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>109400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>108000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>102100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>98400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>92100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>90500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>84500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>83100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>82600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>85300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>81500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>78900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>74500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>73300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>68900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>66300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>62500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>59900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>58300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>56500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>53900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>52600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>178200</v>
+      </c>
+      <c r="E76" s="3">
         <v>150900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>159500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>158300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>154000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>149900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>162700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>169200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>183900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>178800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>175700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>167000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>168900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>162900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>162000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>148100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>148500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>144900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>141300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>134400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>131600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>125700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>123600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>119900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>118300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>117500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>115600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>112600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>96700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E81" s="3">
         <v>3600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>1000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6814,10 +7012,10 @@
         <v>300</v>
       </c>
       <c r="E83" s="3">
+        <v>300</v>
+      </c>
+      <c r="F83" s="3">
         <v>500</v>
-      </c>
-      <c r="F83" s="3">
-        <v>400</v>
       </c>
       <c r="G83" s="3">
         <v>400</v>
@@ -6829,31 +7027,31 @@
         <v>400</v>
       </c>
       <c r="J83" s="3">
+        <v>400</v>
+      </c>
+      <c r="K83" s="3">
         <v>500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-900</v>
-      </c>
-      <c r="P83" s="3">
-        <v>800</v>
       </c>
       <c r="Q83" s="3">
         <v>800</v>
       </c>
       <c r="R83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="S83" s="3">
         <v>500</v>
@@ -6874,7 +7072,7 @@
         <v>500</v>
       </c>
       <c r="Y83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z83" s="3">
         <v>400</v>
@@ -6883,22 +7081,25 @@
         <v>400</v>
       </c>
       <c r="AB83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AC83" s="3">
         <v>500</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>400</v>
       </c>
       <c r="AD83" s="3">
         <v>400</v>
       </c>
       <c r="AE83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF83" s="3">
         <v>500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E89" s="3">
         <v>3400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>8900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-6300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>9300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>5400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>3800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>4900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,8 +7702,9 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7495,88 +7715,91 @@
         <v>-100</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-400</v>
       </c>
       <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-200</v>
       </c>
       <c r="J91" s="3">
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-200</v>
       </c>
       <c r="Z91" s="3">
         <v>-200</v>
       </c>
       <c r="AA91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AB91" s="3">
         <v>-100</v>
       </c>
       <c r="AC91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-27600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-47000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-39600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-134000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>57700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>15200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-86200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>9700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-155500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-54100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-9300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-21700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>4500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-27400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>2500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-71100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-35900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-54100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,13 +8117,14 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -7900,11 +8133,11 @@
         <v>0</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>-3500</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -7912,11 +8145,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -7924,11 +8157,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -7936,11 +8169,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2600</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -7948,11 +8181,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-2200</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -7960,11 +8193,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -7972,13 +8205,16 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100000</v>
+      </c>
+      <c r="E100" s="3">
         <v>24000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-32800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>39600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-70000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>46600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>54600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-12800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>99500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-14100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>231000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>60400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-20500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>6800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>60000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>32100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>57500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>71900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>32200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>41700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>35600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>60400</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-7000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-77600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-59900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-86100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>53100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>50000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>18600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>69200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>28600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>11800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>17200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>7700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>EVBN</t>
   </si>
@@ -656,238 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E8" s="3">
         <v>25200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>23400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>19100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>17500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>17800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>14700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>13400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>12800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>11500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>10900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,8 +1318,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1396,13 +1416,16 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>-100</v>
@@ -1468,7 +1491,7 @@
         <v>-100</v>
       </c>
       <c r="Z15" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA15" s="3">
         <v>0</v>
@@ -1488,11 +1511,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-      <c r="AG15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,103 +1549,107 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E17" s="3">
         <v>11500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>500</v>
-      </c>
-      <c r="O17" s="3">
-        <v>1700</v>
       </c>
       <c r="P17" s="3">
         <v>1700</v>
       </c>
       <c r="Q17" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="R17" s="3">
         <v>2100</v>
       </c>
       <c r="S17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="T17" s="3">
         <v>3800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2900</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>2700</v>
       </c>
       <c r="AA17" s="3">
         <v>2700</v>
       </c>
       <c r="AB17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC17" s="3">
         <v>2200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1627,94 +1657,97 @@
         <v>13700</v>
       </c>
       <c r="E18" s="3">
+        <v>13700</v>
+      </c>
+      <c r="F18" s="3">
         <v>13800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>11900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,198 +1781,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E20" s="3">
         <v>2300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-9500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-11500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-14400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-7100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-8400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E21" s="3">
         <v>16300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>6800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8000</v>
-      </c>
-      <c r="H21" s="3">
-        <v>8200</v>
       </c>
       <c r="I21" s="3">
         <v>8200</v>
       </c>
       <c r="J21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K21" s="3">
         <v>8000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>7400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>4700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>3600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>5000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E23" s="3">
         <v>15900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600</v>
+      </c>
+      <c r="E24" s="3">
         <v>5700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1800</v>
       </c>
       <c r="H24" s="3">
         <v>1800</v>
       </c>
       <c r="I24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J24" s="3">
         <v>2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1800</v>
-      </c>
-      <c r="V24" s="3">
-        <v>1200</v>
       </c>
       <c r="W24" s="3">
         <v>1200</v>
       </c>
       <c r="X24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E26" s="3">
         <v>10200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>5200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E27" s="3">
         <v>10200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2662,17 +2723,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2680,12 +2741,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>9500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>11500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>14400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>7100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>8400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>6700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>7400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>5500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E33" s="3">
         <v>10200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E35" s="3">
         <v>10200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,198 +3524,205 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E41" s="3">
         <v>19700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>15200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>10600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>15400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>14000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>12400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>14000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>13300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>13800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>16800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>172500</v>
+      </c>
+      <c r="E42" s="3">
         <v>11800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>13900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>17400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>12300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>19800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>13500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>94000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>153100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>241000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>185500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>133100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>112000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>89700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>94200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>115700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>44300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>31800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>18300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>49200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>59500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>29300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>18900</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>6800</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>14500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14400</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>5600</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>22400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4300</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3913,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,8 +4110,11 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4103,103 +4208,109 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E48" s="3">
         <v>19200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>20500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>21100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>22200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>22600</v>
-      </c>
-      <c r="S48" s="3">
-        <v>17500</v>
       </c>
       <c r="T48" s="3">
         <v>17500</v>
       </c>
       <c r="U48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="V48" s="3">
         <v>17800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>11000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4207,76 +4318,76 @@
         <v>1900</v>
       </c>
       <c r="E49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F49" s="3">
         <v>13600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>13700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>14000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>13400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>12500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>13000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>13100</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>8500</v>
       </c>
       <c r="AA49" s="3">
         <v>8500</v>
       </c>
       <c r="AB49" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="AC49" s="3">
         <v>8600</v>
@@ -4288,13 +4399,16 @@
         <v>8600</v>
       </c>
       <c r="AF49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AG49" s="3">
         <v>8400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4578,8 +4698,11 @@
       <c r="AG52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2259900</v>
+      </c>
+      <c r="E54" s="3">
         <v>2108700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2174700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2155000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2148300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2178500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2129700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2208400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2240700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2210600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2152100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2160200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2144300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2044100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2057000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2065900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1524800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1460200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1455700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1471100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1456200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1388200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1380900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1346100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1353700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1295600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1220200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1182800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1139700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1100700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1084700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4933,8 +5064,11 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,74 +5162,77 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E59" s="3">
         <v>4100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4600</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5105,8 +5242,8 @@
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5123,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,8 +5358,11 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5230,7 +5373,7 @@
         <v>31200</v>
       </c>
       <c r="F61" s="3">
-        <v>31100</v>
+        <v>31200</v>
       </c>
       <c r="G61" s="3">
         <v>31100</v>
@@ -5242,7 +5385,7 @@
         <v>31100</v>
       </c>
       <c r="J61" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="K61" s="3">
         <v>31000</v>
@@ -5251,7 +5394,7 @@
         <v>31000</v>
       </c>
       <c r="M61" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="N61" s="3">
         <v>30900</v>
@@ -5266,7 +5409,7 @@
         <v>30900</v>
       </c>
       <c r="R61" s="3">
-        <v>11300</v>
+        <v>30900</v>
       </c>
       <c r="S61" s="3">
         <v>11300</v>
@@ -5305,16 +5448,19 @@
         <v>11300</v>
       </c>
       <c r="AE61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AF61" s="3">
         <v>21300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>39500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>62500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2085300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1930400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2023800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1995500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1990000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2024500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1979900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2045700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2071500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2026700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1973200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1984500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1977300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1875200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1894100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1903900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1376700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1311800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1310900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1329800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1321700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1256600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1255300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1222500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1233800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1177300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1102700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1067300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1027000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1004000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>989500</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E72" s="3">
         <v>138600</v>
-      </c>
-      <c r="E72" s="3">
-        <v>128500</v>
       </c>
       <c r="F72" s="3">
         <v>128500</v>
       </c>
       <c r="G72" s="3">
+        <v>128500</v>
+      </c>
+      <c r="H72" s="3">
         <v>123500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>123400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>117300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>115000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>109400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>108000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>102100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>98400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>92100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>90500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>84500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>83100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>82600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>85300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>81500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>78900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>74500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>73300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>68900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>66300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>62500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>59900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>58300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>56500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>53900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>52600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>174600</v>
+      </c>
+      <c r="E76" s="3">
         <v>178200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>150900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>159500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>158300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>154000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>149900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>162700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>169200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>183900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>178800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>175700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>167000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>168900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>162900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>162000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>148100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>148500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>144900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>141300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>134400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>131600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>125700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>123600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>119900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>118300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>117500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>115600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>112600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>96700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E81" s="3">
         <v>10200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7015,10 +7214,10 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
         <v>500</v>
-      </c>
-      <c r="G83" s="3">
-        <v>400</v>
       </c>
       <c r="H83" s="3">
         <v>400</v>
@@ -7030,31 +7229,31 @@
         <v>400</v>
       </c>
       <c r="K83" s="3">
+        <v>400</v>
+      </c>
+      <c r="L83" s="3">
         <v>500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>-200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>-900</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>800</v>
       </c>
       <c r="R83" s="3">
         <v>800</v>
       </c>
       <c r="S83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="T83" s="3">
         <v>500</v>
@@ -7075,7 +7274,7 @@
         <v>500</v>
       </c>
       <c r="Z83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA83" s="3">
         <v>400</v>
@@ -7084,22 +7283,25 @@
         <v>400</v>
       </c>
       <c r="AC83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AD83" s="3">
         <v>500</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>400</v>
       </c>
       <c r="AE83" s="3">
         <v>400</v>
       </c>
       <c r="AF83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG83" s="3">
         <v>500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E89" s="3">
         <v>6100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>9300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>8900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-6300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>9300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>5400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>4900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,13 +7923,14 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
@@ -7718,88 +7939,91 @@
         <v>-100</v>
       </c>
       <c r="G91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-400</v>
       </c>
       <c r="I91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-200</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-200</v>
       </c>
       <c r="AA91" s="3">
         <v>-200</v>
       </c>
       <c r="AB91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AC91" s="3">
         <v>-100</v>
       </c>
       <c r="AD91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E94" s="3">
         <v>92000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>25500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-47000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-16000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-134000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>57700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>15200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-86200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>9700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-155500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-54100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-21700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>4500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-27400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-71100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-35900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-54100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,17 +8351,18 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3600</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -8136,11 +8370,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>-3500</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -8148,11 +8382,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-3300</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -8160,11 +8394,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -8172,11 +8406,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-2600</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -8184,11 +8418,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8196,11 +8430,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -8208,13 +8442,16 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>155800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>24000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-32800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>39600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>46600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>54600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-12800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>99500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>231000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>60400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-20500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>6800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>60000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>57500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>71900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>32200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>41700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>35600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>60400</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-7000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-77600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-59900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-86100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>53100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>50000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>25500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>18600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>69200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-25300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>28600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>11800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>17200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>7700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
   <si>
     <t>EVBN</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E8" s="3">
         <v>25400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>25200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>23400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>22400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>20500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>17500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>18000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>17800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>16000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>15500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>14700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>13400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>11500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1419,8 +1439,11 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1428,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>-100</v>
@@ -1494,7 +1517,7 @@
         <v>-100</v>
       </c>
       <c r="AA15" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1514,11 +1537,14 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-      <c r="AH15" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3">
         <v>11700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>500</v>
-      </c>
-      <c r="P17" s="3">
-        <v>1700</v>
       </c>
       <c r="Q17" s="3">
         <v>1700</v>
       </c>
       <c r="R17" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="S17" s="3">
         <v>2100</v>
       </c>
       <c r="T17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="U17" s="3">
         <v>3800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2900</v>
-      </c>
-      <c r="AA17" s="3">
-        <v>2700</v>
       </c>
       <c r="AB17" s="3">
         <v>2700</v>
       </c>
       <c r="AC17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AD17" s="3">
         <v>2200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>13700</v>
+        <v>14000</v>
       </c>
       <c r="E18" s="3">
         <v>13700</v>
       </c>
       <c r="F18" s="3">
+        <v>13700</v>
+      </c>
+      <c r="G18" s="3">
         <v>13800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>11900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>12600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>11000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-11500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-10500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-14400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-8200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-7100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-8400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-7400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>16300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>6800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8000</v>
-      </c>
-      <c r="I21" s="3">
-        <v>8200</v>
       </c>
       <c r="J21" s="3">
         <v>8200</v>
       </c>
       <c r="K21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="L21" s="3">
         <v>8000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>7400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>4700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>4700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>5000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E23" s="3">
         <v>3000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>15900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>5200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>2500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>900</v>
+      </c>
+      <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1800</v>
       </c>
       <c r="I24" s="3">
         <v>1800</v>
       </c>
       <c r="J24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K24" s="3">
         <v>2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1800</v>
-      </c>
-      <c r="W24" s="3">
-        <v>1200</v>
       </c>
       <c r="X24" s="3">
         <v>1200</v>
       </c>
       <c r="Y24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E26" s="3">
         <v>2300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E27" s="3">
         <v>2300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,17 +2787,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2744,12 +2805,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E32" s="3">
         <v>10700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>11500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>9800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>10500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>14400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>8200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>7100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>8400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>7400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>5500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>6500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E33" s="3">
         <v>2300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E35" s="3">
         <v>2300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,204 +3611,211 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E41" s="3">
         <v>14000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>19700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>17800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>15200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>10600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>14900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>13700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>15400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>11300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>14000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>12400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>13300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>16800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>10800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>118100</v>
+      </c>
+      <c r="E42" s="3">
         <v>172500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>13900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>17400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>13500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>94000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>153100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>241000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>185500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>133100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>112000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>89700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>94200</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>115700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>44300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>31800</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>18300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>49200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>59500</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>29300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>18900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>6800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>14500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>5600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>22400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,8 +4215,11 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4211,106 +4316,112 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E48" s="3">
         <v>19100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>22200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>22600</v>
-      </c>
-      <c r="T48" s="3">
-        <v>17500</v>
       </c>
       <c r="U48" s="3">
         <v>17500</v>
       </c>
       <c r="V48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="W48" s="3">
         <v>17800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>11000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4321,76 +4432,76 @@
         <v>1900</v>
       </c>
       <c r="F49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G49" s="3">
         <v>13600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>13700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>13400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>12500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>13000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>13100</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>8500</v>
       </c>
       <c r="AB49" s="3">
         <v>8500</v>
       </c>
       <c r="AC49" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="AD49" s="3">
         <v>8600</v>
@@ -4402,13 +4513,16 @@
         <v>8600</v>
       </c>
       <c r="AG49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AH49" s="3">
         <v>8400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2257400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2259900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2108700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2174700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2155000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2148300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2178500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2129700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2208400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2240700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2210600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2152100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2160200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2144300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2044100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2057000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2065900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1524800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1460200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1455700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1471100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1456200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1388200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1380900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1346100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1353700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1295600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1220200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1182800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1139700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1100700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1084700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5067,8 +5198,11 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,77 +5299,80 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4600</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5245,8 +5382,8 @@
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,8 +5501,11 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5376,7 +5519,7 @@
         <v>31200</v>
       </c>
       <c r="G61" s="3">
-        <v>31100</v>
+        <v>31200</v>
       </c>
       <c r="H61" s="3">
         <v>31100</v>
@@ -5388,7 +5531,7 @@
         <v>31100</v>
       </c>
       <c r="K61" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="L61" s="3">
         <v>31000</v>
@@ -5397,7 +5540,7 @@
         <v>31000</v>
       </c>
       <c r="N61" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="O61" s="3">
         <v>30900</v>
@@ -5412,7 +5555,7 @@
         <v>30900</v>
       </c>
       <c r="S61" s="3">
-        <v>11300</v>
+        <v>30900</v>
       </c>
       <c r="T61" s="3">
         <v>11300</v>
@@ -5451,16 +5594,19 @@
         <v>11300</v>
       </c>
       <c r="AF61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AG61" s="3">
         <v>21300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>39500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>62500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2079700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2085300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1930400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2023800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1995500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1990000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2024500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1979900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2045700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2071500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2026700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1973200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1984500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1977300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1875200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1894100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1903900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1376700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1311800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1310900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1329800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1321700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1256600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1255300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1222500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1233800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1177300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1102700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1067300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1027000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1004000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>989500</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E72" s="3">
         <v>137200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>138600</v>
-      </c>
-      <c r="F72" s="3">
-        <v>128500</v>
       </c>
       <c r="G72" s="3">
         <v>128500</v>
       </c>
       <c r="H72" s="3">
+        <v>128500</v>
+      </c>
+      <c r="I72" s="3">
         <v>123500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>123400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>117300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>115000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>109400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>108000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>102100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>98400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>92100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>90500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>84500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>83100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>82600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>85300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>81500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>78900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>74500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>73300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>68900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>66300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>62500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>59900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>58300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>56500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>53900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>52600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>177600</v>
+      </c>
+      <c r="E76" s="3">
         <v>174600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>178200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>150900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>159500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>158300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>154000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>149900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>162700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>169200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>183900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>178800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>175700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>167000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>168900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>162900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>162000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>148100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>148500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>144900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>141300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>134400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>131600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>125700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>123600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>119900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>118300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>117500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>115600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>112600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>96700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E81" s="3">
         <v>2300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7217,10 +7416,10 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>400</v>
@@ -7232,31 +7431,31 @@
         <v>400</v>
       </c>
       <c r="L83" s="3">
+        <v>400</v>
+      </c>
+      <c r="M83" s="3">
         <v>500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>-200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>-900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>800</v>
       </c>
       <c r="S83" s="3">
         <v>800</v>
       </c>
       <c r="T83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="U83" s="3">
         <v>500</v>
@@ -7277,7 +7476,7 @@
         <v>500</v>
       </c>
       <c r="AA83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB83" s="3">
         <v>400</v>
@@ -7286,22 +7485,25 @@
         <v>400</v>
       </c>
       <c r="AD83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AE83" s="3">
         <v>500</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>400</v>
       </c>
       <c r="AF83" s="3">
         <v>400</v>
       </c>
       <c r="AG83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AH83" s="3">
         <v>500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>8500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>8900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-6300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>9300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>2600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>4900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,16 +8144,17 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
@@ -7942,88 +8163,91 @@
         <v>-100</v>
       </c>
       <c r="H91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-400</v>
       </c>
       <c r="J91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-300</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-200</v>
       </c>
       <c r="L91" s="3">
         <v>-200</v>
       </c>
       <c r="M91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="N91" s="3">
         <v>-100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AA91" s="3">
-        <v>-200</v>
       </c>
       <c r="AB91" s="3">
         <v>-200</v>
       </c>
       <c r="AC91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AD91" s="3">
         <v>-100</v>
       </c>
       <c r="AE91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E94" s="3">
         <v>1200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>92000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-27600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>25500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-47000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-39600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-134000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>57700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>15200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-86200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>9700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-155500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-54100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-21700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>4500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-27400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-71100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-35900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-54100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8361,11 +8595,11 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>-3600</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
         <v>0</v>
       </c>
@@ -8373,11 +8607,11 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>-3500</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
@@ -8385,11 +8619,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-3300</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -8397,11 +8631,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -8409,11 +8643,11 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-2600</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -8421,11 +8655,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8433,11 +8667,11 @@
         <v>0</v>
       </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
         <v>0</v>
       </c>
@@ -8445,13 +8679,16 @@
         <v>0</v>
       </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E100" s="3">
         <v>155800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>24000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>39600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-70000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>46600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>54600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>99500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-14100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>231000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>60400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-20500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>6800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>60000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>32100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>57500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>71900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>32200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>41700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>35600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>16300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>60400</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-52100</v>
+      </c>
+      <c r="E102" s="3">
         <v>154900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-7000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-77600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-59900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-86100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>53100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>50000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>25500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>69200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-25300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>28600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>2400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>17200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>7700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>EVBN</t>
   </si>
@@ -656,252 +656,259 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>27800</v>
+        <v>17500</v>
       </c>
       <c r="E8" s="3">
-        <v>25400</v>
+        <v>16400</v>
       </c>
       <c r="F8" s="3">
-        <v>25200</v>
+        <v>15900</v>
       </c>
       <c r="G8" s="3">
-        <v>24300</v>
+        <v>32200</v>
       </c>
       <c r="H8" s="3">
-        <v>24000</v>
+        <v>19300</v>
       </c>
       <c r="I8" s="3">
-        <v>23400</v>
+        <v>20500</v>
       </c>
       <c r="J8" s="3">
+        <v>22100</v>
+      </c>
+      <c r="K8" s="3">
         <v>22400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>17500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>20700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>19300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>18000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>17800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>15800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>16000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>15500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>11500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F10" s="3">
+        <v>15900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>32200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>19300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>20500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>22100</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,31 +1358,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1442,31 +1462,34 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="G15" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="H15" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="I15" s="3">
-        <v>-100</v>
+        <v>500</v>
       </c>
       <c r="J15" s="3">
-        <v>-100</v>
+        <v>400</v>
       </c>
       <c r="K15" s="3">
         <v>-100</v>
@@ -1520,7 +1543,7 @@
         <v>-100</v>
       </c>
       <c r="AB15" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1540,11 +1563,14 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-      <c r="AI15" s="3" t="s">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13800</v>
+        <v>12600</v>
       </c>
       <c r="E17" s="3">
-        <v>11700</v>
+        <v>12300</v>
       </c>
       <c r="F17" s="3">
-        <v>11500</v>
+        <v>12600</v>
       </c>
       <c r="G17" s="3">
-        <v>10500</v>
+        <v>15900</v>
       </c>
       <c r="H17" s="3">
-        <v>8200</v>
+        <v>14000</v>
       </c>
       <c r="I17" s="3">
-        <v>5400</v>
+        <v>13700</v>
       </c>
       <c r="J17" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K17" s="3">
         <v>4100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>-300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>500</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>1700</v>
       </c>
       <c r="R17" s="3">
         <v>1700</v>
       </c>
       <c r="S17" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="T17" s="3">
         <v>2100</v>
       </c>
       <c r="U17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="V17" s="3">
         <v>3800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2900</v>
-      </c>
-      <c r="AB17" s="3">
-        <v>2700</v>
       </c>
       <c r="AC17" s="3">
         <v>2700</v>
       </c>
       <c r="AD17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AE17" s="3">
         <v>2200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F18" s="3">
+        <v>3300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>16300</v>
+      </c>
+      <c r="H18" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I18" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K18" s="3">
+        <v>18300</v>
+      </c>
+      <c r="L18" s="3">
+        <v>17900</v>
+      </c>
+      <c r="M18" s="3">
+        <v>17800</v>
+      </c>
+      <c r="N18" s="3">
+        <v>16300</v>
+      </c>
+      <c r="O18" s="3">
+        <v>19300</v>
+      </c>
+      <c r="P18" s="3">
+        <v>19600</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>19100</v>
+      </c>
+      <c r="R18" s="3">
+        <v>16300</v>
+      </c>
+      <c r="S18" s="3">
+        <v>16500</v>
+      </c>
+      <c r="T18" s="3">
+        <v>15700</v>
+      </c>
+      <c r="U18" s="3">
+        <v>15000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>12000</v>
+      </c>
+      <c r="W18" s="3">
+        <v>12900</v>
+      </c>
+      <c r="X18" s="3">
         <v>14000</v>
       </c>
-      <c r="E18" s="3">
-        <v>13700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>13700</v>
-      </c>
-      <c r="G18" s="3">
-        <v>13800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>15800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>18000</v>
-      </c>
-      <c r="J18" s="3">
-        <v>18300</v>
-      </c>
-      <c r="K18" s="3">
-        <v>17900</v>
-      </c>
-      <c r="L18" s="3">
-        <v>17800</v>
-      </c>
-      <c r="M18" s="3">
-        <v>16300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>19300</v>
-      </c>
-      <c r="O18" s="3">
-        <v>19600</v>
-      </c>
-      <c r="P18" s="3">
-        <v>19100</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>16300</v>
-      </c>
-      <c r="R18" s="3">
-        <v>16500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>15700</v>
-      </c>
-      <c r="T18" s="3">
-        <v>15000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>12000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>12900</v>
-      </c>
-      <c r="W18" s="3">
-        <v>14000</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>11900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>12600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>11800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>11000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-10100</v>
+        <v>300</v>
       </c>
       <c r="E20" s="3">
-        <v>-10700</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
-        <v>2300</v>
+        <v>300</v>
       </c>
       <c r="G20" s="3">
-        <v>-8900</v>
+        <v>400</v>
       </c>
       <c r="H20" s="3">
-        <v>-9500</v>
+        <v>500</v>
       </c>
       <c r="I20" s="3">
-        <v>-10400</v>
+        <v>500</v>
       </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-10500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-11500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-10500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-14400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-8200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-7100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-8400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-7400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8000</v>
-      </c>
-      <c r="J21" s="3">
-        <v>8200</v>
       </c>
       <c r="K21" s="3">
         <v>8200</v>
       </c>
       <c r="L21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="M21" s="3">
         <v>8000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>7400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>4700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>4900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,8 +2159,11 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2128,100 +2171,103 @@
         <v>3900</v>
       </c>
       <c r="E23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F23" s="3">
         <v>3000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>5200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>4900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>4500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>4500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2229,100 +2275,103 @@
         <v>900</v>
       </c>
       <c r="E24" s="3">
+        <v>900</v>
+      </c>
+      <c r="F24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1400</v>
-      </c>
-      <c r="I24" s="3">
-        <v>1800</v>
       </c>
       <c r="J24" s="3">
         <v>1800</v>
       </c>
       <c r="K24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L24" s="3">
         <v>2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1800</v>
-      </c>
-      <c r="X24" s="3">
-        <v>1200</v>
       </c>
       <c r="Y24" s="3">
         <v>1200</v>
       </c>
       <c r="Z24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA24" s="3">
         <v>-200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,8 +2471,11 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2431,100 +2483,103 @@
         <v>2900</v>
       </c>
       <c r="E26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F26" s="3">
         <v>2300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2532,100 +2587,103 @@
         <v>2900</v>
       </c>
       <c r="E27" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F27" s="3">
         <v>2300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,17 +2851,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2808,12 +2869,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,109 +3095,115 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>10100</v>
+        <v>-300</v>
       </c>
       <c r="E32" s="3">
-        <v>10700</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
-        <v>-2300</v>
+        <v>-300</v>
       </c>
       <c r="G32" s="3">
-        <v>8900</v>
+        <v>-400</v>
       </c>
       <c r="H32" s="3">
-        <v>9500</v>
+        <v>-500</v>
       </c>
       <c r="I32" s="3">
-        <v>10400</v>
+        <v>-500</v>
       </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>10500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>11500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>10500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>14400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>8200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>7100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>8400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>6700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>7400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>6500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>6500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3138,100 +3211,103 @@
         <v>2900</v>
       </c>
       <c r="E33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F33" s="3">
         <v>2300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,8 +3407,11 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3340,206 +3419,212 @@
         <v>2900</v>
       </c>
       <c r="E35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F35" s="3">
         <v>2300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,233 +3698,240 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>16200</v>
+        <v>128100</v>
       </c>
       <c r="E41" s="3">
+        <v>126300</v>
+      </c>
+      <c r="F41" s="3">
+        <v>178400</v>
+      </c>
+      <c r="G41" s="3">
+        <v>23500</v>
+      </c>
+      <c r="H41" s="3">
+        <v>25300</v>
+      </c>
+      <c r="I41" s="3">
+        <v>25500</v>
+      </c>
+      <c r="J41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="K41" s="3">
+        <v>16800</v>
+      </c>
+      <c r="L41" s="3">
+        <v>14400</v>
+      </c>
+      <c r="M41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="N41" s="3">
+        <v>11400</v>
+      </c>
+      <c r="O41" s="3">
+        <v>9900</v>
+      </c>
+      <c r="P41" s="3">
+        <v>12500</v>
+      </c>
+      <c r="Q41" s="3">
+        <v>14900</v>
+      </c>
+      <c r="R41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="S41" s="3">
+        <v>13700</v>
+      </c>
+      <c r="T41" s="3">
+        <v>15400</v>
+      </c>
+      <c r="U41" s="3">
+        <v>11200</v>
+      </c>
+      <c r="V41" s="3">
+        <v>11300</v>
+      </c>
+      <c r="W41" s="3">
+        <v>10600</v>
+      </c>
+      <c r="X41" s="3">
+        <v>19600</v>
+      </c>
+      <c r="Y41" s="3">
         <v>14000</v>
       </c>
-      <c r="F41" s="3">
-        <v>19700</v>
-      </c>
-      <c r="G41" s="3">
-        <v>17800</v>
-      </c>
-      <c r="H41" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I41" s="3">
-        <v>12300</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="Z41" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AB41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="AC41" s="3">
+        <v>13300</v>
+      </c>
+      <c r="AD41" s="3">
+        <v>11600</v>
+      </c>
+      <c r="AE41" s="3">
+        <v>13800</v>
+      </c>
+      <c r="AF41" s="3">
         <v>16800</v>
       </c>
-      <c r="K41" s="3">
-        <v>14400</v>
-      </c>
-      <c r="L41" s="3">
-        <v>10600</v>
-      </c>
-      <c r="M41" s="3">
-        <v>11400</v>
-      </c>
-      <c r="N41" s="3">
-        <v>9900</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="AG41" s="3">
+        <v>13900</v>
+      </c>
+      <c r="AH41" s="3">
+        <v>10800</v>
+      </c>
+      <c r="AI41" s="3">
         <v>12500</v>
       </c>
-      <c r="P41" s="3">
-        <v>14900</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>10600</v>
-      </c>
-      <c r="R41" s="3">
-        <v>13700</v>
-      </c>
-      <c r="S41" s="3">
-        <v>15400</v>
-      </c>
-      <c r="T41" s="3">
-        <v>11200</v>
-      </c>
-      <c r="U41" s="3">
-        <v>11300</v>
-      </c>
-      <c r="V41" s="3">
-        <v>10600</v>
-      </c>
-      <c r="W41" s="3">
-        <v>19600</v>
-      </c>
-      <c r="X41" s="3">
-        <v>14000</v>
-      </c>
-      <c r="Y41" s="3">
-        <v>12400</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>14000</v>
-      </c>
-      <c r="AA41" s="3">
-        <v>12600</v>
-      </c>
-      <c r="AB41" s="3">
-        <v>13300</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>11600</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>13800</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>16800</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>13900</v>
-      </c>
-      <c r="AG41" s="3">
-        <v>10800</v>
-      </c>
-      <c r="AH41" s="3">
-        <v>12500</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>118100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>11800</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>13900</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>17400</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>12300</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>19800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>13500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>94000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>153100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>241000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>185500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>133100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>112000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>89700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>94200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>115700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>44300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>31800</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>18300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>49200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>59500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>29300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>18900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>6800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>14500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14400</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>5600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>22400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4216,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>128100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>126300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>178400</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>23500</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>25300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>16100</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,31 +4320,34 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>280000</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>271700</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>276500</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>282700</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>340000</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>357800</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>375000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4319,8 +4424,11 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4328,100 +4436,103 @@
         <v>18500</v>
       </c>
       <c r="E48" s="3">
+        <v>18500</v>
+      </c>
+      <c r="F48" s="3">
         <v>19100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>20500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>21100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>22200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>22600</v>
-      </c>
-      <c r="U48" s="3">
-        <v>17500</v>
       </c>
       <c r="V48" s="3">
         <v>17500</v>
       </c>
       <c r="W48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="X48" s="3">
         <v>17800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>11000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4435,76 +4546,76 @@
         <v>1900</v>
       </c>
       <c r="G49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H49" s="3">
         <v>13600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>13700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>13400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>12500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>13000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>13100</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>8500</v>
       </c>
       <c r="AC49" s="3">
         <v>8500</v>
       </c>
       <c r="AD49" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="AE49" s="3">
         <v>8600</v>
@@ -4516,13 +4627,16 @@
         <v>8600</v>
       </c>
       <c r="AH49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AI49" s="3">
         <v>8400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,31 +4840,34 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>86700</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>96400</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>84600</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>60600</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>93400</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>88100</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>85200</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>0</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2280000</v>
+      </c>
+      <c r="E54" s="3">
         <v>2257400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2259900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2108700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2174700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2155000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2148300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2178500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2129700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2208400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2240700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2210600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2152100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2160200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2144300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2044100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2057000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2065900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1524800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1460200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1455700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1471100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1456200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1388200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1380900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1346100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1353700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1295600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1220200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1182800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1139700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1100700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1084700</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,31 +5230,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1900700</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>1891500</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>1891400</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>1718800</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>1805400</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>1786600</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1849900</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5201,31 +5332,34 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>96300</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>129700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>94900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>155500</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>158400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>153200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>77900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,80 +5436,83 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="M59" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="O59" s="3">
+        <v>5200</v>
+      </c>
+      <c r="P59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="R59" s="3">
+        <v>5500</v>
+      </c>
+      <c r="S59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="T59" s="3">
+        <v>5900</v>
+      </c>
+      <c r="U59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="V59" s="3">
         <v>4000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="W59" s="3">
         <v>4200</v>
       </c>
-      <c r="F59" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="X59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="Y59" s="3">
         <v>4400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="Z59" s="3">
         <v>4600</v>
       </c>
-      <c r="I59" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J59" s="3">
-        <v>4700</v>
-      </c>
-      <c r="K59" s="3">
-        <v>4500</v>
-      </c>
-      <c r="L59" s="3">
-        <v>4700</v>
-      </c>
-      <c r="M59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>5200</v>
-      </c>
-      <c r="O59" s="3">
-        <v>5400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>5500</v>
-      </c>
-      <c r="R59" s="3">
-        <v>5700</v>
-      </c>
-      <c r="S59" s="3">
-        <v>5900</v>
-      </c>
-      <c r="T59" s="3">
-        <v>6200</v>
-      </c>
-      <c r="U59" s="3">
-        <v>4000</v>
-      </c>
-      <c r="V59" s="3">
-        <v>4200</v>
-      </c>
-      <c r="W59" s="3">
-        <v>4300</v>
-      </c>
-      <c r="X59" s="3">
-        <v>4400</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>4600</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5385,8 +5522,8 @@
       <c r="AC59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5403,31 +5540,34 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>1997000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>2021200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1986200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>1874300</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>1963900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>1939800</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>1927800</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,37 +5644,40 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>31200</v>
+        <v>75600</v>
       </c>
       <c r="E61" s="3">
-        <v>31200</v>
+        <v>42200</v>
       </c>
       <c r="F61" s="3">
-        <v>31200</v>
+        <v>78400</v>
       </c>
       <c r="G61" s="3">
-        <v>31200</v>
+        <v>34300</v>
       </c>
       <c r="H61" s="3">
-        <v>31100</v>
+        <v>41800</v>
       </c>
       <c r="I61" s="3">
-        <v>31100</v>
+        <v>42100</v>
       </c>
       <c r="J61" s="3">
-        <v>31100</v>
+        <v>47000</v>
       </c>
       <c r="K61" s="3">
         <v>31100</v>
       </c>
       <c r="L61" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="M61" s="3">
         <v>31000</v>
@@ -5543,7 +5686,7 @@
         <v>31000</v>
       </c>
       <c r="O61" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="P61" s="3">
         <v>30900</v>
@@ -5558,7 +5701,7 @@
         <v>30900</v>
       </c>
       <c r="T61" s="3">
-        <v>11300</v>
+        <v>30900</v>
       </c>
       <c r="U61" s="3">
         <v>11300</v>
@@ -5597,39 +5740,42 @@
         <v>11300</v>
       </c>
       <c r="AG61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AH61" s="3">
         <v>21300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>39500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>62500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>16300</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>20700</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>21800</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>18200</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>13600</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>15200</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2094200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2079700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2085300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1930400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2023800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1995500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1990000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2024500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1979900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2045700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2071500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2026700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1973200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1984500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1977300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1875200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1894100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1903900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1376700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1311800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1310900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1329800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1321700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1256600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1255300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1222500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1233800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1177300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1102700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1067300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1027000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1004000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>989500</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E72" s="3">
         <v>140100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>137200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>138600</v>
-      </c>
-      <c r="G72" s="3">
-        <v>128500</v>
       </c>
       <c r="H72" s="3">
         <v>128500</v>
       </c>
       <c r="I72" s="3">
+        <v>128500</v>
+      </c>
+      <c r="J72" s="3">
         <v>123500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>123400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>117300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>115000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>109400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>108000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>102100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>98400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>92100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>90500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>84500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>83100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>82600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>85300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>81500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>78900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>74500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>73300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>68900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>66300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>62500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>59900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>58300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>56500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>53900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>52600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>185800</v>
+      </c>
+      <c r="E76" s="3">
         <v>177600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>174600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>178200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>150900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>159500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>158300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>154000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>149900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>162700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>169200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>183900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>178800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>175700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>167000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>168900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>162900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>162000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>148100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>148500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>144900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>141300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>134400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>131600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>125700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>123600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>119900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>118300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>117500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>115600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>112600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>96700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,114 +7346,120 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7272,100 +7467,103 @@
         <v>2900</v>
       </c>
       <c r="E81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F81" s="3">
         <v>2300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,16 +7599,17 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
@@ -7419,10 +7618,10 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="I83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J83" s="3">
         <v>400</v>
@@ -7434,31 +7633,31 @@
         <v>400</v>
       </c>
       <c r="M83" s="3">
+        <v>400</v>
+      </c>
+      <c r="N83" s="3">
         <v>500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>-900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>800</v>
       </c>
       <c r="T83" s="3">
         <v>800</v>
       </c>
       <c r="U83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="V83" s="3">
         <v>500</v>
@@ -7479,7 +7678,7 @@
         <v>500</v>
       </c>
       <c r="AB83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AC83" s="3">
         <v>400</v>
@@ -7488,22 +7687,25 @@
         <v>400</v>
       </c>
       <c r="AE83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AF83" s="3">
         <v>500</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>400</v>
       </c>
       <c r="AG83" s="3">
         <v>400</v>
       </c>
       <c r="AH83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AI83" s="3">
         <v>500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>9300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>8500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>8900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-6300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>4100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>9300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>5400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>4900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
-        <v>-100</v>
-      </c>
       <c r="G91" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-400</v>
       </c>
       <c r="K91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-200</v>
       </c>
       <c r="M91" s="3">
         <v>-200</v>
       </c>
       <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-200</v>
       </c>
       <c r="AC91" s="3">
         <v>-200</v>
       </c>
       <c r="AD91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AE91" s="3">
         <v>-100</v>
       </c>
       <c r="AF91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-39000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>1200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>92000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-27600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>25500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-47000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-134000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>57700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>15200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-86200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>9700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-155500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-54100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-21700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-35500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>4500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>2500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-71100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-35900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-54100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8595,26 +8829,26 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-3600</v>
+        <v>3600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K96" s="3">
         <v>-3500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
@@ -8622,11 +8856,11 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-3300</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -8634,11 +8868,11 @@
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-3100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -8646,11 +8880,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-2600</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -8658,11 +8892,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8670,11 +8904,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -8682,13 +8916,16 @@
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>155800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>24000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-32800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>39600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-70000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-27600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>46600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>54600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>99500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-14100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>231000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>60400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-20500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>6800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>60000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>32100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>57500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>71900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>32200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>41700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>35600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>16300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>60400</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-52100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>154900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-7000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-77600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-59900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-86100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>53100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>50000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>69200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>4500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-25300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>28600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>17200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>7700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EVBN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
   <si>
     <t>EVBN</t>
   </si>
@@ -656,259 +656,265 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E8" s="3">
         <v>17500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>32200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>19300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>20500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>20700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>19300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>18000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>17800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>17100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>16000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>16300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>15500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>15300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>12600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>10900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>10200</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1011,35 +1017,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E10" s="3">
         <v>17500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>16400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>32200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>20500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,17 +1377,20 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1387,8 +1406,8 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1465,8 +1484,11 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1486,13 +1508,13 @@
         <v>300</v>
       </c>
       <c r="I15" s="3">
+        <v>300</v>
+      </c>
+      <c r="J15" s="3">
         <v>500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>-100</v>
       </c>
       <c r="L15" s="3">
         <v>-100</v>
@@ -1546,7 +1568,7 @@
         <v>-100</v>
       </c>
       <c r="AC15" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1566,11 +1588,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
-      <c r="AJ15" s="3" t="s">
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E17" s="3">
         <v>12600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>15900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>-300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>500</v>
-      </c>
-      <c r="R17" s="3">
-        <v>1700</v>
       </c>
       <c r="S17" s="3">
         <v>1700</v>
       </c>
       <c r="T17" s="3">
-        <v>2100</v>
+        <v>1700</v>
       </c>
       <c r="U17" s="3">
         <v>2100</v>
       </c>
       <c r="V17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="W17" s="3">
         <v>3800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>3300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>3600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2900</v>
-      </c>
-      <c r="AC17" s="3">
-        <v>2700</v>
       </c>
       <c r="AD17" s="3">
         <v>2700</v>
       </c>
       <c r="AE17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AF17" s="3">
         <v>2200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="3">
         <v>4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>16300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>8000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>11900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>12600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>11800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>11500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>11000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,13 +1882,14 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
@@ -1865,10 +1898,10 @@
         <v>300</v>
       </c>
       <c r="G20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3">
         <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>500</v>
       </c>
       <c r="I20" s="3">
         <v>500</v>
@@ -1877,189 +1910,195 @@
         <v>500</v>
       </c>
       <c r="K20" s="3">
+        <v>500</v>
+      </c>
+      <c r="L20" s="3">
         <v>-10500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-11500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-10800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-9600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-10500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-14400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-8200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-7400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-7000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-8400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-7400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-6300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-6500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-5300</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E21" s="3">
         <v>4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>16300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>8200</v>
       </c>
       <c r="L21" s="3">
         <v>8200</v>
       </c>
       <c r="M21" s="3">
+        <v>8200</v>
+      </c>
+      <c r="N21" s="3">
         <v>8000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>7400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>4700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>5600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>5400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>4700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>4900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>3900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>5000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,216 +2201,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3900</v>
+        <v>3500</v>
       </c>
       <c r="E23" s="3">
         <v>3900</v>
       </c>
       <c r="F23" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G23" s="3">
         <v>3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>4900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>4900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>4300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>4500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>2500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>900</v>
+        <v>-200</v>
       </c>
       <c r="E24" s="3">
         <v>900</v>
       </c>
       <c r="F24" s="3">
+        <v>900</v>
+      </c>
+      <c r="G24" s="3">
         <v>600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>1800</v>
       </c>
       <c r="K24" s="3">
         <v>1800</v>
       </c>
       <c r="L24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M24" s="3">
         <v>2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1800</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>1200</v>
       </c>
       <c r="Z24" s="3">
         <v>1200</v>
       </c>
       <c r="AA24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="E26" s="3">
         <v>2900</v>
       </c>
       <c r="F26" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G26" s="3">
         <v>2300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>6300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>2600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="E27" s="3">
         <v>2900</v>
       </c>
       <c r="F27" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G27" s="3">
         <v>2300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>6300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>2600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,17 +2914,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
@@ -2872,12 +2932,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,13 +3164,16 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>-400</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
@@ -3113,10 +3182,10 @@
         <v>-300</v>
       </c>
       <c r="G32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3">
         <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-500</v>
       </c>
       <c r="I32" s="3">
         <v>-500</v>
@@ -3125,189 +3194,195 @@
         <v>-500</v>
       </c>
       <c r="K32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L32" s="3">
         <v>10500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>11500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>10800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>9600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>10500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>14400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>8200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>7100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>7400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>7000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>8400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>6700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>6500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>6400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>7400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>6500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>6300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>5500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>6500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="E33" s="3">
         <v>2900</v>
       </c>
       <c r="F33" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G33" s="3">
         <v>2300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>6300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>3800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>2600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="E35" s="3">
         <v>2900</v>
       </c>
       <c r="F35" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G35" s="3">
         <v>2300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>6300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>3800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>2600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E41" s="3">
         <v>128100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>126300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>178400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>25300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>25500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>10600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>10600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>15400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>11200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>11300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>14000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>14000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>12600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>10800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>14800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3830,85 +3919,88 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>19800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>13500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>94000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>153100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>241000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>185500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>133100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>112000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>89700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>94200</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>115700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>44300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>31800</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>18300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>49200</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>59500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>29300</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>18900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>6800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>14500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>14400</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>5600</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>5400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>22400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>9100</v>
       </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3933,8 +4025,8 @@
       <c r="J43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,8 +4239,8 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4219,35 +4317,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1827500</v>
+      </c>
+      <c r="E46" s="3">
         <v>128100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>126300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>178400</v>
       </c>
-      <c r="G46" s="3">
-        <v>23500</v>
-      </c>
       <c r="H46" s="3">
+        <v>1745300</v>
+      </c>
+      <c r="I46" s="3">
         <v>25300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>25500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>16100</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,35 +4424,38 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>269200</v>
+      </c>
+      <c r="E47" s="3">
         <v>280000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>271700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>276500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>282700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>340000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>357800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>375000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4427,117 +4531,123 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>18500</v>
+        <v>18000</v>
       </c>
       <c r="E48" s="3">
         <v>18500</v>
       </c>
       <c r="F48" s="3">
+        <v>18500</v>
+      </c>
+      <c r="G48" s="3">
         <v>19100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>19900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>21100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>22200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>22600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>23900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22600</v>
-      </c>
-      <c r="V48" s="3">
-        <v>17500</v>
       </c>
       <c r="W48" s="3">
         <v>17500</v>
       </c>
       <c r="X48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="Y48" s="3">
         <v>17800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>14400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>14700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>10400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>11000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>11100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>11300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1900</v>
+        <v>1800</v>
       </c>
       <c r="E49" s="3">
         <v>1900</v>
@@ -4549,76 +4659,76 @@
         <v>1900</v>
       </c>
       <c r="H49" s="3">
+        <v>1900</v>
+      </c>
+      <c r="I49" s="3">
         <v>13600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>13700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>13800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>14000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>14100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>14200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>14300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>14700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>14800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>13400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>12500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>12700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>12800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>12900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>13000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>13100</v>
-      </c>
-      <c r="AC49" s="3">
-        <v>8500</v>
       </c>
       <c r="AD49" s="3">
         <v>8500</v>
       </c>
       <c r="AE49" s="3">
-        <v>8600</v>
+        <v>8500</v>
       </c>
       <c r="AF49" s="3">
         <v>8600</v>
@@ -4630,13 +4740,16 @@
         <v>8600</v>
       </c>
       <c r="AI49" s="3">
+        <v>8600</v>
+      </c>
+      <c r="AJ49" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,35 +4959,38 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E52" s="3">
         <v>86700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>96400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>84600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>60600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>93400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>88100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>85200</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
         <v>0</v>
       </c>
@@ -4947,8 +5066,11 @@
       <c r="AJ52" s="3">
         <v>0</v>
       </c>
+      <c r="AK52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2187500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2280000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2257400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2259900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2108700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2174700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2155000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2148300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2178500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2129700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2208400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2240700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2210600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2152100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2160200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2144300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2044100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2057000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2065900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1524800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1460200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1455700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1471100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1456200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1388200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>1380900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1346100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1353700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1295600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1220200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1182800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1139700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1100700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1084700</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,35 +5360,36 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1866500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1900700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1891500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1891400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1718800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1805400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1786600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1849900</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
@@ -5335,35 +5465,38 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E58" s="3">
         <v>96300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>129700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>94900</v>
       </c>
-      <c r="G58" s="3">
-        <v>155500</v>
-      </c>
       <c r="H58" s="3">
+        <v>154600</v>
+      </c>
+      <c r="I58" s="3">
         <v>158400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>153200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>77900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5439,8 +5572,11 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5465,57 +5601,57 @@
       <c r="J59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
         <v>4700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>5200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>5400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>5700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>5500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>5700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4600</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AB59" s="3" t="s">
         <v>5</v>
       </c>
@@ -5525,8 +5661,8 @@
       <c r="AD59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5543,35 +5679,38 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1954100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1997000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2021200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1986200</v>
       </c>
-      <c r="G60" s="3">
-        <v>1874300</v>
-      </c>
       <c r="H60" s="3">
+        <v>1873300</v>
+      </c>
+      <c r="I60" s="3">
         <v>1963900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1939800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1927800</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5647,40 +5786,43 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E61" s="3">
         <v>75600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>78400</v>
       </c>
-      <c r="G61" s="3">
-        <v>34300</v>
-      </c>
       <c r="H61" s="3">
+        <v>35300</v>
+      </c>
+      <c r="I61" s="3">
         <v>41800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>42100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>47000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>31100</v>
       </c>
       <c r="L61" s="3">
         <v>31100</v>
       </c>
       <c r="M61" s="3">
-        <v>31000</v>
+        <v>31100</v>
       </c>
       <c r="N61" s="3">
         <v>31000</v>
@@ -5689,7 +5831,7 @@
         <v>31000</v>
       </c>
       <c r="P61" s="3">
-        <v>30900</v>
+        <v>31000</v>
       </c>
       <c r="Q61" s="3">
         <v>30900</v>
@@ -5704,7 +5846,7 @@
         <v>30900</v>
       </c>
       <c r="U61" s="3">
-        <v>11300</v>
+        <v>30900</v>
       </c>
       <c r="V61" s="3">
         <v>11300</v>
@@ -5743,43 +5885,46 @@
         <v>11300</v>
       </c>
       <c r="AH61" s="3">
+        <v>11300</v>
+      </c>
+      <c r="AI61" s="3">
         <v>21300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>39500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>62500</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E62" s="3">
         <v>21600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>16300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>13600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>15200</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2004300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2094200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2079700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2085300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1930400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2023800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1995500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1990000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2024500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1979900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2045700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2071500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2026700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1973200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1984500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1977300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1875200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1894100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1903900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1376700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1311800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1310900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1329800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1321700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1256600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1255300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1222500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1233800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1177300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1102700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1067300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1027000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1004000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>989500</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>142900</v>
+      </c>
+      <c r="E72" s="3">
         <v>139300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>140100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>137200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>138600</v>
-      </c>
-      <c r="H72" s="3">
-        <v>128500</v>
       </c>
       <c r="I72" s="3">
         <v>128500</v>
       </c>
       <c r="J72" s="3">
+        <v>128500</v>
+      </c>
+      <c r="K72" s="3">
         <v>123500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>123400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>117300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>115000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>109400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>108000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>102100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>98400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>92100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>90500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>84500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>83100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>82600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>85300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>81500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>78900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>74500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>73300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>68900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>66300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>62500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>59900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>58300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>56500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>53900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>52600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>50300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E76" s="3">
         <v>185800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>177600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>174600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>178200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>150900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>159500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>158300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>154000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>149900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>162700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>169200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>183900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>178800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>175700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>167000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>168900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>162900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>162000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>148100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>148500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>144900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>141300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>134400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>131600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>125700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>123600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>119900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>118300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>117500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>115600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>112600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>96700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>95200</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="E81" s="3">
         <v>2900</v>
       </c>
       <c r="F81" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G81" s="3">
         <v>2300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>6300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>3800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>2600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,19 +7797,20 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -7624,7 +7822,7 @@
         <v>300</v>
       </c>
       <c r="J83" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="K83" s="3">
         <v>400</v>
@@ -7636,31 +7834,31 @@
         <v>400</v>
       </c>
       <c r="N83" s="3">
+        <v>400</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>-900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>800</v>
       </c>
       <c r="U83" s="3">
         <v>800</v>
       </c>
       <c r="V83" s="3">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="W83" s="3">
         <v>500</v>
@@ -7681,7 +7879,7 @@
         <v>500</v>
       </c>
       <c r="AC83" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AD83" s="3">
         <v>400</v>
@@ -7690,22 +7888,25 @@
         <v>400</v>
       </c>
       <c r="AF83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AG83" s="3">
         <v>500</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>400</v>
       </c>
       <c r="AH83" s="3">
         <v>400</v>
       </c>
       <c r="AI83" s="3">
+        <v>400</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E89" s="3">
         <v>11900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-8600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>9300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>8500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>8900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-6300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>6800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>9300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>5400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-100</v>
       </c>
       <c r="I91" s="3">
         <v>-100</v>
       </c>
       <c r="J91" s="3">
-        <v>-400</v>
+        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-400</v>
       </c>
       <c r="L91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-200</v>
       </c>
       <c r="N91" s="3">
         <v>-200</v>
       </c>
       <c r="O91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P91" s="3">
         <v>-100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-200</v>
       </c>
       <c r="AD91" s="3">
         <v>-200</v>
       </c>
       <c r="AE91" s="3">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="AF91" s="3">
         <v>-100</v>
       </c>
       <c r="AG91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>92000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>25500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-47000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-16000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-134000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>57700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>15200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>9700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-155500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-54100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-21700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-35500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>4500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>2500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-62200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-71100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-35900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-59000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-20500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-54100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,38 +9052,39 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>3600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>3600</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>3600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="K96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L96" s="3">
         <v>-3500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -8859,11 +9092,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3300</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -8871,11 +9104,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-3100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8883,11 +9116,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-2600</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8895,11 +9128,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -8907,11 +9140,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -8919,13 +9152,16 @@
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,112 +9478,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="E100" s="3">
         <v>9000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>155800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-100000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>24000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>4200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-32800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>39600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-70000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>46600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>54600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>7900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>99500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-12900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>231000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>60400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>6800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>60000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>32100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>57500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>71900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>32200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>41700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>35600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>60400</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9366,8 +9614,8 @@
       <c r="J101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9444,108 +9692,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-85400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-52100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>154900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-7000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-77600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-59900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-86100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>53100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>50000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>25500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-6000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>69200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-25300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>28600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>17200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-6100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>7700</v>
       </c>
     </row>
